--- a/artfynd/A 44632-2023 artfynd.xlsx
+++ b/artfynd/A 44632-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44632-2023 artfynd.xlsx
+++ b/artfynd/A 44632-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81447421</v>
+        <v>121687735</v>
       </c>
       <c r="B2" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Harbacken, V, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582163.0572373224</v>
+        <v>582452</v>
       </c>
       <c r="R2" t="n">
-        <v>6558825.968068391</v>
+        <v>6558874</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +747,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-10-05</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-10-05</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,31 +777,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kryptogamer i Södermanlands län</t>
-        </is>
-      </c>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>81447422</v>
+        <v>81447421</v>
       </c>
       <c r="B3" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582288.8707446539</v>
+        <v>582163</v>
       </c>
       <c r="R3" t="n">
-        <v>6558877.409754273</v>
+        <v>6558826</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -864,19 +857,9 @@
           <t>2018-10-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-10-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,6 +887,214 @@
           <t>Kryptogamer i Södermanlands län</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>81447422</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Harbacken, V, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>582289</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6558877</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sköldinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kryptogamer i Södermanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121215425</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fyrsjön 600m NO, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>582514</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6558847</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44632-2023 artfynd.xlsx
+++ b/artfynd/A 44632-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121687735</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
           <t>Kryptogamer i Södermanlands län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81447421</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Kryptogamer i Södermanlands län</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81447422</t>
         </is>
       </c>
     </row>
@@ -1095,8 +1115,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121215425</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>